--- a/data/trans_dic/P44A$sangre-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 50,69</t>
+          <t>9,98; 51,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 34,25</t>
+          <t>4,98; 33,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,98; 68,9</t>
+          <t>53,89; 69,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,34</t>
+          <t>0,0; 39,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,54; 80,12</t>
+          <t>63,68; 80,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 40,66</t>
+          <t>8,95; 39,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 27,68</t>
+          <t>3,82; 25,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,74; 70,85</t>
+          <t>59,94; 71,51</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,2</t>
+          <t>0,0; 38,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 33,53</t>
+          <t>3,87; 34,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,11; 75,2</t>
+          <t>56,45; 75,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,02; 79,44</t>
+          <t>61,07; 79,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,99</t>
+          <t>0,0; 29,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 28,05</t>
+          <t>3,48; 29,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,18; 74,07</t>
+          <t>60,72; 74,6</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 57,71</t>
+          <t>19,63; 57,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,0</t>
+          <t>0,0; 24,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,27; 97,95</t>
+          <t>59,4; 97,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,81</t>
+          <t>0,0; 46,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,16; 84,94</t>
+          <t>62,4; 84,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 47,64</t>
+          <t>14,74; 45,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,32</t>
+          <t>0,0; 22,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,23; 97,01</t>
+          <t>63,81; 97,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,49</t>
+          <t>0,0; 19,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 18,81</t>
+          <t>1,98; 18,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,72; 73,09</t>
+          <t>60,19; 72,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,41</t>
+          <t>0,0; 30,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 32,2</t>
+          <t>3,85; 33,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,65; 74,02</t>
+          <t>58,16; 73,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,06</t>
+          <t>0,0; 16,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,61</t>
+          <t>4,05; 17,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,67; 71,51</t>
+          <t>61,88; 71,6</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 32,26</t>
+          <t>3,69; 29,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,88; 75,2</t>
+          <t>56,02; 75,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>0,0; 22,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,56</t>
+          <t>0,0; 26,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,57; 77,16</t>
+          <t>64,7; 77,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,56</t>
+          <t>0,0; 16,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 20,69</t>
+          <t>3,76; 20,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63,35; 74,23</t>
+          <t>63,91; 74,38</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,32; 100,0</t>
+          <t>36,6; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 25,57</t>
+          <t>3,08; 24,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 25,6</t>
+          <t>2,7; 24,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64,05; 76,12</t>
+          <t>63,86; 76,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 25,57</t>
+          <t>3,08; 24,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 25,6</t>
+          <t>2,7; 24,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64,46; 76,1</t>
+          <t>64,21; 75,53</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 28,27</t>
+          <t>11,18; 27,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 16,74</t>
+          <t>6,56; 16,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,92; 90,7</t>
+          <t>63,81; 89,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 15,45</t>
+          <t>3,9; 15,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 15,22</t>
+          <t>4,28; 14,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,53; 73,67</t>
+          <t>67,55; 73,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,78</t>
+          <t>9,27; 19,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,78</t>
+          <t>6,56; 14,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,82; 86,41</t>
+          <t>66,83; 86,32</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1809; 9709</t>
+          <t>1911; 9844</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1184; 10595</t>
+          <t>1540; 10334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69256; 88401</t>
+          <t>69144; 89361</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6064</t>
+          <t>0; 5323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2078</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46809; 59019</t>
+          <t>46906; 58979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2997; 13225</t>
+          <t>2911; 12708</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1562; 11634</t>
+          <t>1605; 10530</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120649; 143084</t>
+          <t>121051; 144425</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6037</t>
+          <t>0; 6176</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1051; 9036</t>
+          <t>1043; 9172</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46459; 62266</t>
+          <t>46735; 62664</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1931</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29407; 38921</t>
+          <t>29922; 38910</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6622</t>
+          <t>0; 7130</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>980; 9050</t>
+          <t>1122; 9631</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79309; 97612</t>
+          <t>80018; 98311</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5372; 16902</t>
+          <t>5750; 16907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7594</t>
+          <t>0; 7230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>198928; 323308</t>
+          <t>196053; 321241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5104</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20259; 27682</t>
+          <t>20337; 27520</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5850; 19146</t>
+          <t>5925; 18154</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7429</t>
+          <t>0; 8095</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>232944; 351794</t>
+          <t>231406; 352437</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6697</t>
+          <t>0; 6992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>973; 9282</t>
+          <t>976; 9057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95046; 116325</t>
+          <t>95805; 116090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4405</t>
+          <t>0; 4413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>921; 7827</t>
+          <t>936; 8020</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50995; 63278</t>
+          <t>49723; 62901</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>972; 7637</t>
+          <t>0; 8489</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2836; 12972</t>
+          <t>2984; 12885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>150875; 174940</t>
+          <t>151403; 175179</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1758</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>879; 7498</t>
+          <t>858; 6947</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37164; 50017</t>
+          <t>37262; 50287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6176</t>
+          <t>0; 6063</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7006</t>
+          <t>0; 7136</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71562; 85513</t>
+          <t>71703; 85462</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6926</t>
+          <t>0; 5907</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1835; 10481</t>
+          <t>1902; 10284</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112351; 131642</t>
+          <t>113332; 131904</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1100; 3886</t>
+          <t>1422; 3886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>952; 8172</t>
+          <t>984; 7767</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1124; 10095</t>
+          <t>1064; 9627</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76720; 91178</t>
+          <t>76499; 91123</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>952; 8172</t>
+          <t>984; 7767</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1124; 10095</t>
+          <t>1064; 9627</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79719; 94112</t>
+          <t>79412; 93412</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12122; 30912</t>
+          <t>12226; 29752</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10801; 26726</t>
+          <t>10482; 26977</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>492661; 699068</t>
+          <t>491811; 693458</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4246; 16376</t>
+          <t>4137; 16119</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5091; 17486</t>
+          <t>4919; 16366</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>318300; 347255</t>
+          <t>318404; 347236</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19794; 40444</t>
+          <t>19971; 41717</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18047; 37851</t>
+          <t>18002; 38796</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>829998; 1073250</t>
+          <t>830030; 1072139</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$sangre-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 51,39</t>
+          <t>9,38; 51,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 33,4</t>
+          <t>4,98; 35,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,89; 69,65</t>
+          <t>53,57; 68,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,8</t>
+          <t>0,0; 45,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,68; 80,07</t>
+          <t>63,14; 79,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 39,07</t>
+          <t>9,08; 39,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 25,06</t>
+          <t>2,73; 25,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,94; 71,51</t>
+          <t>59,66; 70,85</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,05</t>
+          <t>0,0; 33,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 34,04</t>
+          <t>4,07; 32,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,45; 75,68</t>
+          <t>54,58; 73,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,07; 79,42</t>
+          <t>62,1; 80,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,06</t>
+          <t>0,0; 25,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 29,85</t>
+          <t>3,27; 29,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,72; 74,6</t>
+          <t>60,21; 74,21</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 57,73</t>
+          <t>17,54; 56,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,76</t>
+          <t>0,0; 28,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,4; 97,33</t>
+          <t>54,44; 71,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,93</t>
+          <t>0,0; 52,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,4; 84,45</t>
+          <t>61,48; 83,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,74; 45,17</t>
+          <t>15,2; 46,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,14</t>
+          <t>0,0; 20,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,81; 97,18</t>
+          <t>58,16; 73,41</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,3</t>
+          <t>0,0; 17,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 18,35</t>
+          <t>2,26; 18,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,19; 72,94</t>
+          <t>59,46; 72,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,46</t>
+          <t>0,0; 37,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 33,0</t>
+          <t>3,81; 30,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,16; 73,57</t>
+          <t>58,4; 72,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,74</t>
+          <t>1,95; 16,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 17,49</t>
+          <t>3,79; 17,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,88; 71,6</t>
+          <t>60,47; 71,1</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -1123,49 +1123,49 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 29,89</t>
+          <t>3,74; 30,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,02; 75,6</t>
+          <t>54,54; 75,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>0,0; 22,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,03</t>
+          <t>0,0; 24,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,7; 77,11</t>
+          <t>65,01; 76,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,69</t>
+          <t>0,0; 17,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 20,3</t>
+          <t>3,56; 21,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63,91; 74,38</t>
+          <t>62,92; 73,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,6; 100,0</t>
+          <t>21,79; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 24,3</t>
+          <t>3,09; 25,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 24,41</t>
+          <t>2,75; 24,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,86; 76,07</t>
+          <t>64,31; 76,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 24,3</t>
+          <t>3,09; 25,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 24,41</t>
+          <t>2,75; 24,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64,21; 75,53</t>
+          <t>64,19; 75,96</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 27,2</t>
+          <t>11,44; 28,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,89</t>
+          <t>6,16; 16,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,81; 89,98</t>
+          <t>60,45; 67,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 15,21</t>
+          <t>4,56; 15,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,24</t>
+          <t>3,8; 14,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,55; 73,67</t>
+          <t>67,33; 73,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,27; 19,37</t>
+          <t>9,63; 18,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,13</t>
+          <t>6,54; 13,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,83; 86,32</t>
+          <t>64,8; 69,62</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79338</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53287</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132625</t>
+          <t>143583</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1639,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1911; 9844</t>
+          <t>1796; 9953</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1540; 10334</t>
+          <t>1540; 10972</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69144; 89361</t>
+          <t>73040; 93883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5323</t>
+          <t>0; 6020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46906; 58979</t>
+          <t>52465; 65834</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2911; 12708</t>
+          <t>2953; 12924</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1605; 10530</t>
+          <t>1146; 10693</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121051; 144425</t>
+          <t>130902; 155470</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>55510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89323</t>
+          <t>95311</t>
         </is>
       </c>
     </row>
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6176</t>
+          <t>0; 5442</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1043; 9172</t>
+          <t>1097; 8738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46735; 62664</t>
+          <t>46926; 63538</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29922; 38910</t>
+          <t>34162; 44459</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7130</t>
+          <t>0; 6291</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1122; 9631</t>
+          <t>1056; 9582</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80018; 98311</t>
+          <t>84893; 104619</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298372</t>
+          <t>57527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>322851</t>
+          <t>84347</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5750; 16907</t>
+          <t>5137; 16475</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7230</t>
+          <t>0; 8306</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196053; 321241</t>
+          <t>49783; 65568</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5116</t>
+          <t>0; 5735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20337; 27520</t>
+          <t>22147; 30210</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5925; 18154</t>
+          <t>6109; 18688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 8095</t>
+          <t>0; 7330</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>231406; 352437</t>
+          <t>74133; 93566</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106499</t>
+          <t>115020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57201</t>
+          <t>61526</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>163700</t>
+          <t>176545</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6992</t>
+          <t>0; 6399</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>976; 9057</t>
+          <t>1115; 8998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95805; 116090</t>
+          <t>103397; 126324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4413</t>
+          <t>0; 5499</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>936; 8020</t>
+          <t>925; 7496</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49723; 62901</t>
+          <t>54614; 68244</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 8489</t>
+          <t>990; 8250</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2984; 12885</t>
+          <t>2794; 12571</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>151403; 175179</t>
+          <t>161717; 190134</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78339</t>
+          <t>85151</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>122642</t>
+          <t>133263</t>
         </is>
       </c>
     </row>
@@ -2296,49 +2296,49 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>858; 6947</t>
+          <t>868; 7163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37262; 50287</t>
+          <t>39803; 54768</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6063</t>
+          <t>0; 6060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7136</t>
+          <t>0; 6583</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71703; 85462</t>
+          <t>78043; 92060</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5907</t>
+          <t>0; 6124</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1902; 10284</t>
+          <t>1803; 10957</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>113332; 131904</t>
+          <t>121461; 142787</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84361</t>
+          <t>93460</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>87236</t>
+          <t>96285</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1422; 3886</t>
+          <t>839; 3850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>984; 7767</t>
+          <t>987; 8095</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1064; 9627</t>
+          <t>1086; 9605</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76499; 91123</t>
+          <t>85030; 100500</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>984; 7767</t>
+          <t>987; 8095</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1064; 9627</t>
+          <t>1086; 9605</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79412; 93412</t>
+          <t>87350; 103358</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586037</t>
+          <t>363080</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>332340</t>
+          <t>366253</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>918377</t>
+          <t>729332</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12226; 29752</t>
+          <t>12508; 30662</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10482; 26977</t>
+          <t>9844; 25970</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>491811; 693458</t>
+          <t>341212; 383738</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4137; 16119</t>
+          <t>4833; 16555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4919; 16366</t>
+          <t>4361; 17108</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>318404; 347236</t>
+          <t>350082; 381415</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19971; 41717</t>
+          <t>20742; 40238</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18002; 38796</t>
+          <t>17948; 37311</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>830030; 1072139</t>
+          <t>702705; 754963</t>
         </is>
       </c>
     </row>
